--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733C692E-F0ED-4C1A-BECC-6D347778CBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EDF1D3-3A8A-43E6-A118-BAD55432DEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,7 +333,7 @@
     <t>https://forms.gle/sozZnsJmkSaZ3uv49</t>
   </si>
   <si>
-    <t>5th August</t>
+    <t>11th August</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EDF1D3-3A8A-43E6-A118-BAD55432DEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA1934E-D33B-4B94-99C2-267DEFD3D0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,7 +333,7 @@
     <t>https://forms.gle/sozZnsJmkSaZ3uv49</t>
   </si>
   <si>
-    <t>11th August</t>
+    <t>12th August</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA1934E-D33B-4B94-99C2-267DEFD3D0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1880C628-A074-453B-9B30-9A2A27F31260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,7 +333,7 @@
     <t>https://forms.gle/sozZnsJmkSaZ3uv49</t>
   </si>
   <si>
-    <t>12th August</t>
+    <t>1th August</t>
   </si>
 </sst>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1880C628-A074-453B-9B30-9A2A27F31260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DBE9A9-8708-4381-AAB3-6961F27D43A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -333,7 +333,7 @@
     <t>https://forms.gle/sozZnsJmkSaZ3uv49</t>
   </si>
   <si>
-    <t>1th August</t>
+    <t>14th August</t>
   </si>
 </sst>
 </file>
@@ -669,42 +669,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.54296875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +799,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -816,7 +816,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -833,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -850,7 +850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -870,7 +870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -913,7 +913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -939,7 +939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2026</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DBE9A9-8708-4381-AAB3-6961F27D43A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95E34FB-A83D-494C-A71A-4F3825181F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95E34FB-A83D-494C-A71A-4F3825181F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F365B0-5D32-4B6C-A1A2-EC162DACFDDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="104">
   <si>
     <t>Year</t>
   </si>
@@ -334,6 +334,15 @@
   </si>
   <si>
     <t>14th August</t>
+  </si>
+  <si>
+    <t>12th EFSPI regulatory statistics workshop</t>
+  </si>
+  <si>
+    <t>[here](2027.html)</t>
+  </si>
+  <si>
+    <t>15-16 (or 17) September 2027</t>
   </si>
 </sst>
 </file>
@@ -668,43 +677,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE13"/>
+  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="35" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="36.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="39.6328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +808,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -816,7 +825,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -833,7 +842,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -850,7 +859,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -870,7 +879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -890,7 +899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -913,7 +922,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -939,7 +948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -965,7 +974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -1006,7 +1015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1089,13 +1098,10 @@
         <v>459403</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2026</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
       <c r="C12" t="s">
         <v>89</v>
       </c>
@@ -1161,6 +1167,35 @@
       </c>
       <c r="Y12" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2027</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F365B0-5D32-4B6C-A1A2-EC162DACFDDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC5DAF3-AA7B-43BA-AB9F-910D8C773870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="105">
   <si>
     <t>Year</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>15-16 (or 17) September 2027</t>
+  </si>
+  <si>
+    <t>Boehringer Ingelheim</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1124,7 @@
         <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>98</v>
@@ -1189,7 +1192,7 @@
         <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>98</v>
